--- a/artfynd/A 23145-2026 artfynd.xlsx
+++ b/artfynd/A 23145-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134619355</v>
+        <v>134637829</v>
       </c>
       <c r="B7" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,37 +1259,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487226</v>
+        <v>487308</v>
       </c>
       <c r="R7" t="n">
-        <v>6979405</v>
+        <v>6979499</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,55 +1348,55 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134618070</v>
+        <v>134619355</v>
       </c>
       <c r="B8" t="n">
-        <v>80382</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487272</v>
+        <v>487226</v>
       </c>
       <c r="R8" t="n">
-        <v>6979652</v>
+        <v>6979405</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,12 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På asp i äldre barrblandskog</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,65 +1450,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134618233</v>
+        <v>134637833</v>
       </c>
       <c r="B9" t="n">
-        <v>80382</v>
+        <v>79992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med isidier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487309</v>
+        <v>487223</v>
       </c>
       <c r="R9" t="n">
-        <v>6979649</v>
+        <v>6979401</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,12 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp (45 cm dbh) i äldre barrblandskog</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,19 +1557,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134618643</v>
+        <v>134618070</v>
       </c>
       <c r="B10" t="n">
         <v>80382</v>
@@ -1613,21 +1598,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487316</v>
+        <v>487272</v>
       </c>
       <c r="R10" t="n">
-        <v>6979512</v>
+        <v>6979652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1639,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1649,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (55 cm dbh) i gammal barrblandskog</t>
+          <t>På asp i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,35 +1681,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134618244</v>
+        <v>134618233</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>80382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med isidier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
@@ -1771,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1813,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134618346</v>
+        <v>134618643</v>
       </c>
       <c r="B12" t="n">
-        <v>80492</v>
+        <v>80382</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,34 +1809,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487351</v>
+        <v>487316</v>
       </c>
       <c r="R12" t="n">
-        <v>6979646</v>
+        <v>6979512</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,12 +1883,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På litet block i äldre barrblandskog</t>
+          <t>På bark på stam av levande asp (55 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,48 +1915,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134623836</v>
+        <v>134618244</v>
       </c>
       <c r="B13" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487317</v>
+        <v>487309</v>
       </c>
       <c r="R13" t="n">
-        <v>6979452</v>
+        <v>6979649</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1995,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På asp (45 cm dbh) i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,65 +2015,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134623743</v>
+        <v>134618346</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487295</v>
+        <v>487351</v>
       </c>
       <c r="R14" t="n">
-        <v>6979474</v>
+        <v>6979646</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,12 +2107,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall som är mer än 150 år</t>
+          <t>På litet block i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,69 +2127,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134623869</v>
+        <v>134623836</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>80492</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487389</v>
+        <v>487317</v>
       </c>
       <c r="R15" t="n">
-        <v>6979494</v>
+        <v>6979452</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,12 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>+2 vinterståndare</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134618835</v>
+        <v>134637826</v>
       </c>
       <c r="B16" t="n">
-        <v>107695</v>
+        <v>80492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,37 +2257,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221705</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Melampyrum pratense</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487284</v>
+        <v>487355</v>
       </c>
       <c r="R16" t="n">
-        <v>6979439</v>
+        <v>6979504</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2340,7 +2316,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2326,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,69 +2346,60 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134618455</v>
+        <v>134623743</v>
       </c>
       <c r="B17" t="n">
-        <v>106309</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487359</v>
+        <v>487295</v>
       </c>
       <c r="R17" t="n">
-        <v>6979628</v>
+        <v>6979474</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2461,7 +2428,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,12 +2438,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I äldre barrblandskog</t>
+          <t>Ringhack på tall som är mer än 150 år</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,60 +2458,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134618336</v>
+        <v>134637821</v>
       </c>
       <c r="B18" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487347</v>
+        <v>487291</v>
       </c>
       <c r="R18" t="n">
-        <v>6979670</v>
+        <v>6979650</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2540,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,12 +2550,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,60 +2570,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134618965</v>
+        <v>134637822</v>
       </c>
       <c r="B19" t="n">
-        <v>99872</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222316</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klotstarr</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carex globularis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487284</v>
+        <v>487293</v>
       </c>
       <c r="R19" t="n">
-        <v>6979439</v>
+        <v>6979657</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2685,7 +2652,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2662,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, äldre spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,55 +2687,55 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134618485</v>
+        <v>134637823</v>
       </c>
       <c r="B20" t="n">
-        <v>80444</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487357</v>
+        <v>487313</v>
       </c>
       <c r="R20" t="n">
-        <v>6979618</v>
+        <v>6979635</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2792,7 +2764,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2802,12 +2774,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På grov sälglåga i äldre barrblandskog</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,60 +2794,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134619363</v>
+        <v>134637824</v>
       </c>
       <c r="B21" t="n">
-        <v>79396</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>260591</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487218</v>
+        <v>487359</v>
       </c>
       <c r="R21" t="n">
-        <v>6979401</v>
+        <v>6979505</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,7 +2876,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2914,12 +2886,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal senvuxen tall på talludde vid myr</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,60 +2906,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134624193</v>
+        <v>134637825</v>
       </c>
       <c r="B22" t="n">
-        <v>83358</v>
+        <v>58131</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>103023</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487554</v>
+        <v>487356</v>
       </c>
       <c r="R22" t="n">
-        <v>6979356</v>
+        <v>6979504</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3016,7 +2988,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3026,12 +2998,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>1 ex lockläte</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3046,60 +3018,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134624138</v>
+        <v>134623869</v>
       </c>
       <c r="B23" t="n">
-        <v>80382</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487554</v>
+        <v>487389</v>
       </c>
       <c r="R23" t="n">
-        <v>6979356</v>
+        <v>6979494</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3128,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3138,12 +3119,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>+2 vinterståndare</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,65 +3139,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134624216</v>
+        <v>134618835</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>107695</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221705</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487587</v>
+        <v>487284</v>
       </c>
       <c r="R24" t="n">
-        <v>6979388</v>
+        <v>6979439</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3245,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3255,12 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,22 +3246,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134624375</v>
+        <v>134618455</v>
       </c>
       <c r="B25" t="n">
-        <v>106324</v>
+        <v>106309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3298,34 +3269,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487599</v>
+        <v>487359</v>
       </c>
       <c r="R25" t="n">
-        <v>6979420</v>
+        <v>6979628</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3357,7 +3342,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3352,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På marken i tallskog</t>
+          <t>I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,39 +3377,39 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134619985</v>
+        <v>134618336</v>
       </c>
       <c r="B26" t="n">
-        <v>93271</v>
+        <v>99217</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3434,13 +3419,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487125</v>
+        <v>487347</v>
       </c>
       <c r="R26" t="n">
-        <v>6979494</v>
+        <v>6979670</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3469,7 +3454,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3479,7 +3464,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,60 +3484,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134623562</v>
+        <v>134637820</v>
       </c>
       <c r="B27" t="n">
-        <v>93271</v>
+        <v>99217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487067</v>
+        <v>487275</v>
       </c>
       <c r="R27" t="n">
-        <v>6979518</v>
+        <v>6979637</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3576,7 +3566,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3586,7 +3576,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,55 +3596,55 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134620673</v>
+        <v>134637827</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>99217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487001</v>
+        <v>487313</v>
       </c>
       <c r="R28" t="n">
-        <v>6979537</v>
+        <v>6979509</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3683,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3693,12 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>45 cm långa bålar på gammal tall</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,69 +3698,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134620688</v>
+        <v>134618965</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>99872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>222316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Klotstarr</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carex globularis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486981</v>
+        <v>487284</v>
       </c>
       <c r="R29" t="n">
-        <v>6979523</v>
+        <v>6979439</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3804,7 +3780,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3790,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,48 +3817,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134621129</v>
+        <v>134637828</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>78382</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486977</v>
+        <v>487317</v>
       </c>
       <c r="R30" t="n">
-        <v>6979380</v>
+        <v>6979494</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3911,7 +3887,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,12 +3897,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,57 +3912,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134621774</v>
+        <v>134618485</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>80444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487007</v>
+        <v>487357</v>
       </c>
       <c r="R31" t="n">
-        <v>6979324</v>
+        <v>6979618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4023,7 +3994,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,12 +4004,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal tallskog</t>
+          <t>På grov sälglåga i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4058,17 +4029,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134620466</v>
+        <v>134619363</v>
       </c>
       <c r="B32" t="n">
-        <v>78776</v>
+        <v>79396</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,21 +4047,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>260591</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4100,10 +4071,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487031</v>
+        <v>487218</v>
       </c>
       <c r="R32" t="n">
-        <v>6979572</v>
+        <v>6979401</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4135,7 +4106,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4145,12 +4116,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>På gammal senvuxen tall på talludde vid myr</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4170,17 +4141,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134620802</v>
+        <v>134637834</v>
       </c>
       <c r="B33" t="n">
-        <v>83358</v>
+        <v>79396</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4188,37 +4159,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>260591</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486980</v>
+        <v>487224</v>
       </c>
       <c r="R33" t="n">
-        <v>6979507</v>
+        <v>6979397</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4247,7 +4218,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4257,12 +4228,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4277,19 +4243,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134620885</v>
+        <v>134624193</v>
       </c>
       <c r="B34" t="n">
         <v>83358</v>
@@ -4320,17 +4286,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486951</v>
+        <v>487554</v>
       </c>
       <c r="R34" t="n">
-        <v>6979512</v>
+        <v>6979356</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4359,7 +4325,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,12 +4335,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal sumpgranskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,32 +4367,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134620305</v>
+        <v>134624138</v>
       </c>
       <c r="B35" t="n">
-        <v>79130</v>
+        <v>80382</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4436,10 +4402,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487031</v>
+        <v>487554</v>
       </c>
       <c r="R35" t="n">
-        <v>6979572</v>
+        <v>6979356</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4471,7 +4437,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4481,12 +4447,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,10 +4479,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134621634</v>
+        <v>134637854</v>
       </c>
       <c r="B36" t="n">
-        <v>79130</v>
+        <v>93271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4524,37 +4490,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487047</v>
+        <v>487622</v>
       </c>
       <c r="R36" t="n">
-        <v>6979362</v>
+        <v>6979627</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4583,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4593,12 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,60 +4574,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134620077</v>
+        <v>134637857</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487120</v>
+        <v>487632</v>
       </c>
       <c r="R37" t="n">
-        <v>6979507</v>
+        <v>6979790</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4695,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4705,12 +4666,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På rotben på gammal tallåga i gammal hällmarkstallskog</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,60 +4681,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134620174</v>
+        <v>134637858</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487035</v>
+        <v>487643</v>
       </c>
       <c r="R38" t="n">
-        <v>6979565</v>
+        <v>6979820</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4807,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4817,12 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,19 +4788,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134620386</v>
+        <v>134637853</v>
       </c>
       <c r="B39" t="n">
         <v>79992</v>
@@ -4880,17 +4831,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487031</v>
+        <v>487630</v>
       </c>
       <c r="R39" t="n">
-        <v>6979572</v>
+        <v>6979597</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4919,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4929,12 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4949,60 +4895,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134621552</v>
+        <v>134637851</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487037</v>
+        <v>487604</v>
       </c>
       <c r="R40" t="n">
-        <v>6979375</v>
+        <v>6979461</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5031,7 +4977,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5041,12 +4987,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5061,60 +5002,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134621604</v>
+        <v>134637852</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80492</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487047</v>
+        <v>487630</v>
       </c>
       <c r="R41" t="n">
-        <v>6979362</v>
+        <v>6979578</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5143,7 +5084,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5153,12 +5094,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,65 +5109,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134620794</v>
+        <v>134637863</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486975</v>
+        <v>487854</v>
       </c>
       <c r="R42" t="n">
-        <v>6979500</v>
+        <v>6979801</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5260,7 +5191,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5270,12 +5201,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack och födosöksspår på gammal död gran</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5295,14 +5221,14 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134620818</v>
+        <v>134624216</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -5338,17 +5264,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486974</v>
+        <v>487587</v>
       </c>
       <c r="R43" t="n">
-        <v>6979501</v>
+        <v>6979388</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5377,7 +5303,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5387,12 +5313,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5407,19 +5333,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134621085</v>
+        <v>134637856</v>
       </c>
       <c r="B44" t="n">
         <v>57975</v>
@@ -5448,24 +5374,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486979</v>
+        <v>487583</v>
       </c>
       <c r="R44" t="n">
-        <v>6979382</v>
+        <v>6979673</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5494,7 +5415,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5504,12 +5425,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack, rikligt, på gammal tall i kanten mot sumpskog</t>
+          <t>Äldre ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5524,60 +5445,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134621423</v>
+        <v>134637859</v>
       </c>
       <c r="B45" t="n">
-        <v>111153</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220240</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487018</v>
+        <v>487804</v>
       </c>
       <c r="R45" t="n">
-        <v>6979338</v>
+        <v>6979778</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5606,7 +5527,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5616,12 +5537,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal stavatallskog</t>
+          <t>Ringhack på gammal tall, äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5636,74 +5557,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134621349</v>
+        <v>134637860</v>
       </c>
       <c r="B46" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486975</v>
+        <v>487809</v>
       </c>
       <c r="R46" t="n">
-        <v>6979371</v>
+        <v>6979778</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5732,7 +5639,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,12 +5649,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>17 skott, varav ett blommande, på marken i gammal barrblandskog</t>
+          <t>Ringhack på gammal tall, äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5762,60 +5669,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134622212</v>
+        <v>134637861</v>
       </c>
       <c r="B47" t="n">
-        <v>106358</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221157</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487160</v>
+        <v>487825</v>
       </c>
       <c r="R47" t="n">
-        <v>6979297</v>
+        <v>6979774</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5844,7 +5751,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5854,7 +5761,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tall, äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5874,55 +5786,55 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134622977</v>
+        <v>134637862</v>
       </c>
       <c r="B48" t="n">
-        <v>106309</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487004</v>
+        <v>487825</v>
       </c>
       <c r="R48" t="n">
-        <v>6979263</v>
+        <v>6979802</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5951,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5961,7 +5873,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5981,55 +5898,55 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134620740</v>
+        <v>134637864</v>
       </c>
       <c r="B49" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487009</v>
+        <v>487898</v>
       </c>
       <c r="R49" t="n">
-        <v>6979527</v>
+        <v>6979887</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6058,7 +5975,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6068,12 +5985,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På marken i i gammal tallskog på udde mot myr</t>
+          <t>Äldre ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6088,44 +6005,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134620155</v>
+        <v>134624375</v>
       </c>
       <c r="B50" t="n">
-        <v>79131</v>
+        <v>106324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6135,10 +6052,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487035</v>
+        <v>487599</v>
       </c>
       <c r="R50" t="n">
-        <v>6979565</v>
+        <v>6979420</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6170,7 +6087,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6180,12 +6097,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe</t>
+          <t>På marken i tallskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6205,17 +6122,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134620355</v>
+        <v>134637848</v>
       </c>
       <c r="B51" t="n">
-        <v>79131</v>
+        <v>79405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6223,37 +6140,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487031</v>
+        <v>487137</v>
       </c>
       <c r="R51" t="n">
-        <v>6979572</v>
+        <v>6979293</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6282,7 +6199,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6292,12 +6209,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6312,22 +6224,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134621567</v>
+        <v>134637842</v>
       </c>
       <c r="B52" t="n">
-        <v>79131</v>
+        <v>91974</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,37 +6247,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487037</v>
+        <v>486973</v>
       </c>
       <c r="R52" t="n">
-        <v>6979375</v>
+        <v>6979366</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6394,7 +6306,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6404,12 +6316,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6424,22 +6331,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134621619</v>
+        <v>134619985</v>
       </c>
       <c r="B53" t="n">
-        <v>79131</v>
+        <v>93271</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6447,21 +6354,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6471,13 +6378,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487047</v>
+        <v>487125</v>
       </c>
       <c r="R53" t="n">
-        <v>6979362</v>
+        <v>6979494</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6506,7 +6413,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6516,12 +6423,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6536,22 +6438,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134622346</v>
+        <v>134623562</v>
       </c>
       <c r="B54" t="n">
-        <v>79645</v>
+        <v>93271</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6559,37 +6461,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229338</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårtig dynlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Micarea elachista</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Körb.) Coppins &amp; R.Sant.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487155</v>
+        <v>487067</v>
       </c>
       <c r="R54" t="n">
-        <v>6979276</v>
+        <v>6979518</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6618,7 +6520,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6628,12 +6530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På tallhögstubbe/ dimensionsavverkningsstubbe i gammal tallskog</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6648,60 +6545,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134620767</v>
+        <v>134637841</v>
       </c>
       <c r="B55" t="n">
-        <v>79396</v>
+        <v>91937</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>260591</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487013</v>
+        <v>486988</v>
       </c>
       <c r="R55" t="n">
-        <v>6979545</v>
+        <v>6979418</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6730,7 +6627,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6740,12 +6637,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gammal tall i gammal tallskog</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6760,57 +6652,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134621877</v>
+        <v>134620673</v>
       </c>
       <c r="B56" t="n">
-        <v>79396</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487072</v>
+        <v>487001</v>
       </c>
       <c r="R56" t="n">
-        <v>6979275</v>
+        <v>6979537</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6842,7 +6734,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6852,12 +6744,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På äldre gran i gammal tallskog</t>
+          <t>45 cm långa bålar på gammal tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6884,48 +6776,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134621948</v>
+        <v>134620688</v>
       </c>
       <c r="B57" t="n">
-        <v>79396</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487125</v>
+        <v>486981</v>
       </c>
       <c r="R57" t="n">
-        <v>6979267</v>
+        <v>6979523</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6954,7 +6855,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6964,12 +6865,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På död tall i äldre tallskog</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6984,15 +6880,4347 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134621129</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>486977</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6979380</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gammal gran i gransumpskog</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>Fredrik Jonsson</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134621774</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>487007</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6979324</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gammal tall i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134637844</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>486955</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6979311</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134620466</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>487031</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6979572</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe i gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134620802</v>
+      </c>
+      <c r="B62" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>486980</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6979507</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134620885</v>
+      </c>
+      <c r="B63" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>486951</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6979512</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal sumpgranskog</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134620305</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>487031</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6979572</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134621634</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>487047</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6979362</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134637836</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>486956</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6979505</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134637846</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>487136</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6979298</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134620077</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>487120</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6979507</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rotben på gammal tallåga i gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134620174</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>487035</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6979565</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134620386</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>487031</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6979572</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134621552</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>487037</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6979375</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134621604</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>487047</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6979362</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134637835</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>486956</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6979505</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134637839</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>486984</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6979419</v>
+      </c>
+      <c r="S74" t="n">
+        <v>7</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134637845</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>487137</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6979297</v>
+      </c>
+      <c r="S75" t="n">
+        <v>7</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>134620794</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>486975</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6979500</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack och födosöksspår på gammal död gran</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>134620818</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>486974</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6979501</v>
+      </c>
+      <c r="S77" t="n">
+        <v>6</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>134621085</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>486979</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6979382</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack, rikligt, på gammal tall i kanten mot sumpskog</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134621423</v>
+      </c>
+      <c r="B79" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>487018</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6979338</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt på marken i gammal stavatallskog</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134621349</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>486975</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6979371</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>17 skott, varav ett blommande, på marken i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134622212</v>
+      </c>
+      <c r="B81" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>487160</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6979297</v>
+      </c>
+      <c r="S81" t="n">
+        <v>8</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>134622977</v>
+      </c>
+      <c r="B82" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>487004</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6979263</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134620740</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>487009</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6979527</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På marken i i gammal tallskog på udde mot myr</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134637849</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>487158</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6979235</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134637850</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99848</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>487015</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6979263</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134620155</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>487035</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6979565</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134620355</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>487031</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6979572</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134621567</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>487037</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6979375</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134621619</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>487047</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6979362</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134637837</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>486956</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6979505</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>134637840</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>486991</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6979419</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134637847</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>487136</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6979298</v>
+      </c>
+      <c r="S92" t="n">
+        <v>3</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>134622346</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79645</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229338</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vårtig dynlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Micarea elachista</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Körb.) Coppins &amp; R.Sant.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>487155</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6979276</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På tallhögstubbe/ dimensionsavverkningsstubbe i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134620767</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>487013</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6979545</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På gammal tall i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134621877</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>487072</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6979275</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På äldre gran i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134621948</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>487125</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6979267</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På död tall i äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23145-2026 artfynd.xlsx
+++ b/artfynd/A 23145-2026 artfynd.xlsx
@@ -8438,7 +8438,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 23145-2026 artfynd.xlsx
+++ b/artfynd/A 23145-2026 artfynd.xlsx
@@ -8438,7 +8438,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 23145-2026 artfynd.xlsx
+++ b/artfynd/A 23145-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,53 +2241,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134623743</v>
+        <v>134637824</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487295</v>
+        <v>487359</v>
       </c>
       <c r="R16" t="n">
-        <v>6979474</v>
+        <v>6979505</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2316,7 +2311,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2326,12 +2321,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall som är mer än 150 år</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,34 +2346,34 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134637821</v>
+        <v>134637825</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>58131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2393,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487291</v>
+        <v>487356</v>
       </c>
       <c r="R17" t="n">
-        <v>6979650</v>
+        <v>6979504</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2428,7 +2423,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2438,12 +2433,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>1 ex lockläte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,48 +2465,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134637822</v>
+        <v>134623869</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487293</v>
+        <v>487389</v>
       </c>
       <c r="R18" t="n">
-        <v>6979657</v>
+        <v>6979494</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2540,7 +2544,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2550,12 +2554,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran, äldre spår</t>
+          <t>+2 vinterståndare</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,55 +2579,55 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134637823</v>
+        <v>134618835</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>107695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221705</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487313</v>
+        <v>487284</v>
       </c>
       <c r="R19" t="n">
-        <v>6979635</v>
+        <v>6979439</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2652,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2662,12 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,17 +2686,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134637824</v>
+        <v>134618455</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>106309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,37 +2704,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>487359</v>
       </c>
       <c r="R20" t="n">
-        <v>6979505</v>
+        <v>6979628</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2764,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2774,12 +2787,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,22 +2807,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134637825</v>
+        <v>134618336</v>
       </c>
       <c r="B21" t="n">
-        <v>58131</v>
+        <v>99217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,37 +2830,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103023</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487356</v>
+        <v>487347</v>
       </c>
       <c r="R21" t="n">
-        <v>6979504</v>
+        <v>6979670</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2876,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2886,12 +2899,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 ex lockläte</t>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,69 +2919,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134623869</v>
+        <v>134637820</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487389</v>
+        <v>487275</v>
       </c>
       <c r="R22" t="n">
-        <v>6979494</v>
+        <v>6979637</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,12 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>+2 vinterståndare</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,17 +3031,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134618835</v>
+        <v>134637827</v>
       </c>
       <c r="B23" t="n">
-        <v>107695</v>
+        <v>99217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3050,37 +3049,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221705</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Melampyrum pratense</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487284</v>
+        <v>487313</v>
       </c>
       <c r="R23" t="n">
-        <v>6979439</v>
+        <v>6979509</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3109,7 +3108,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3118,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,17 +3138,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134618455</v>
+        <v>134618965</v>
       </c>
       <c r="B24" t="n">
-        <v>106309</v>
+        <v>99872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,51 +3156,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>222316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Klotstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carex globularis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487359</v>
+        <v>487284</v>
       </c>
       <c r="R24" t="n">
-        <v>6979628</v>
+        <v>6979439</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3230,7 +3215,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3240,12 +3225,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I äldre barrblandskog</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,60 +3240,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134618336</v>
+        <v>134637828</v>
       </c>
       <c r="B25" t="n">
-        <v>99217</v>
+        <v>78382</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487347</v>
+        <v>487317</v>
       </c>
       <c r="R25" t="n">
-        <v>6979670</v>
+        <v>6979494</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,7 +3322,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3352,12 +3332,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,22 +3347,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134637820</v>
+        <v>134618485</v>
       </c>
       <c r="B26" t="n">
-        <v>99217</v>
+        <v>80444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3395,37 +3370,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>229748</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487275</v>
+        <v>487357</v>
       </c>
       <c r="R26" t="n">
-        <v>6979637</v>
+        <v>6979618</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3454,7 +3429,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3464,7 +3439,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På grov sälglåga i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,60 +3459,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134637827</v>
+        <v>134619363</v>
       </c>
       <c r="B27" t="n">
-        <v>99217</v>
+        <v>79396</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>260591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487313</v>
+        <v>487218</v>
       </c>
       <c r="R27" t="n">
-        <v>6979509</v>
+        <v>6979401</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,7 +3541,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3551,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen tall på talludde vid myr</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,60 +3571,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134618965</v>
+        <v>134637834</v>
       </c>
       <c r="B28" t="n">
-        <v>99872</v>
+        <v>79396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222316</v>
+        <v>260591</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klotstarr</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carex globularis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487284</v>
+        <v>487224</v>
       </c>
       <c r="R28" t="n">
-        <v>6979439</v>
+        <v>6979397</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3668,7 +3653,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3678,7 +3663,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,17 +3683,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134637828</v>
+        <v>134624022</v>
       </c>
       <c r="B29" t="n">
-        <v>78382</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,37 +3701,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487317</v>
+        <v>487514</v>
       </c>
       <c r="R29" t="n">
-        <v>6979494</v>
+        <v>6979419</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,7 +3760,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3785,7 +3770,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3805,55 +3795,55 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134618485</v>
+        <v>134637854</v>
       </c>
       <c r="B30" t="n">
-        <v>80444</v>
+        <v>93271</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229748</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487357</v>
+        <v>487622</v>
       </c>
       <c r="R30" t="n">
-        <v>6979618</v>
+        <v>6979627</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3882,7 +3872,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3892,12 +3882,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På grov sälglåga i äldre barrblandskog</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3912,60 +3897,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134619363</v>
+        <v>134637857</v>
       </c>
       <c r="B31" t="n">
-        <v>79396</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487218</v>
+        <v>487632</v>
       </c>
       <c r="R31" t="n">
-        <v>6979401</v>
+        <v>6979790</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3994,7 +3979,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4004,12 +3989,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen tall på talludde vid myr</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4024,44 +4004,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134637834</v>
+        <v>134637858</v>
       </c>
       <c r="B32" t="n">
-        <v>79396</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4071,10 +4051,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487224</v>
+        <v>487643</v>
       </c>
       <c r="R32" t="n">
-        <v>6979397</v>
+        <v>6979820</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4106,7 +4086,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4116,7 +4096,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4143,10 +4123,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134624022</v>
+        <v>134624193</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>83358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4154,21 +4134,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4178,13 +4158,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487514</v>
+        <v>487554</v>
       </c>
       <c r="R33" t="n">
-        <v>6979419</v>
+        <v>6979356</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4213,7 +4193,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4223,12 +4203,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4243,22 +4223,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134637854</v>
+        <v>134637853</v>
       </c>
       <c r="B34" t="n">
-        <v>93271</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,21 +4246,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4290,13 +4270,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>487622</v>
+        <v>487630</v>
       </c>
       <c r="R34" t="n">
-        <v>6979627</v>
+        <v>6979597</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4362,48 +4342,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134637857</v>
+        <v>134624138</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>80382</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487632</v>
+        <v>487554</v>
       </c>
       <c r="R35" t="n">
-        <v>6979790</v>
+        <v>6979356</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4432,7 +4412,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4442,7 +4422,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4457,44 +4442,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134637858</v>
+        <v>134637851</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>80492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4504,13 +4489,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487643</v>
+        <v>487604</v>
       </c>
       <c r="R36" t="n">
-        <v>6979820</v>
+        <v>6979461</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4539,7 +4524,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4549,7 +4534,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4576,48 +4561,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134624193</v>
+        <v>134637852</v>
       </c>
       <c r="B37" t="n">
-        <v>83358</v>
+        <v>80492</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487554</v>
+        <v>487630</v>
       </c>
       <c r="R37" t="n">
-        <v>6979356</v>
+        <v>6979578</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4646,7 +4631,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4656,12 +4641,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4676,44 +4656,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134637853</v>
+        <v>134637863</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>80492</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4723,13 +4703,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487630</v>
+        <v>487854</v>
       </c>
       <c r="R38" t="n">
-        <v>6979597</v>
+        <v>6979801</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4758,7 +4738,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4768,7 +4748,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4795,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134624138</v>
+        <v>134624375</v>
       </c>
       <c r="B39" t="n">
-        <v>80382</v>
+        <v>106324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4806,21 +4786,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4830,10 +4810,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487554</v>
+        <v>487599</v>
       </c>
       <c r="R39" t="n">
-        <v>6979356</v>
+        <v>6979420</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4865,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4875,12 +4855,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På marken i tallskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4907,32 +4887,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134637851</v>
+        <v>134637848</v>
       </c>
       <c r="B40" t="n">
-        <v>80492</v>
+        <v>79405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4942,13 +4922,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487604</v>
+        <v>487137</v>
       </c>
       <c r="R40" t="n">
-        <v>6979461</v>
+        <v>6979293</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4977,7 +4957,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4987,7 +4967,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5014,32 +4994,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134637852</v>
+        <v>134637842</v>
       </c>
       <c r="B41" t="n">
-        <v>80492</v>
+        <v>91974</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5049,13 +5029,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487630</v>
+        <v>486973</v>
       </c>
       <c r="R41" t="n">
-        <v>6979578</v>
+        <v>6979366</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5084,7 +5064,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5094,7 +5074,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5121,48 +5101,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134637863</v>
+        <v>134619985</v>
       </c>
       <c r="B42" t="n">
-        <v>80492</v>
+        <v>93271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487854</v>
+        <v>487125</v>
       </c>
       <c r="R42" t="n">
-        <v>6979801</v>
+        <v>6979494</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5191,7 +5171,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5201,7 +5181,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5221,17 +5201,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134624216</v>
+        <v>134623562</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>93271</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5239,42 +5219,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487587</v>
+        <v>487067</v>
       </c>
       <c r="R43" t="n">
-        <v>6979388</v>
+        <v>6979518</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5303,7 +5278,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5313,12 +5288,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal levande gran i gammal granskog</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,44 +5303,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134637856</v>
+        <v>134637841</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>91937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5380,13 +5350,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487583</v>
+        <v>486988</v>
       </c>
       <c r="R44" t="n">
-        <v>6979673</v>
+        <v>6979418</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5415,7 +5385,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5425,12 +5395,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal tall</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5457,48 +5422,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134637859</v>
+        <v>134620673</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487804</v>
+        <v>487001</v>
       </c>
       <c r="R45" t="n">
-        <v>6979778</v>
+        <v>6979537</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5527,7 +5492,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5537,12 +5502,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall, äldre</t>
+          <t>45 cm långa bålar på gammal tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5557,60 +5522,69 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134637860</v>
+        <v>134620688</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487809</v>
+        <v>486981</v>
       </c>
       <c r="R46" t="n">
-        <v>6979778</v>
+        <v>6979523</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5639,7 +5613,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5649,12 +5623,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tall, äldre</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5674,55 +5643,55 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134637861</v>
+        <v>134621129</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487825</v>
+        <v>486977</v>
       </c>
       <c r="R47" t="n">
-        <v>6979774</v>
+        <v>6979380</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5751,7 +5720,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5761,12 +5730,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tall, äldre</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5781,60 +5750,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134637862</v>
+        <v>134621774</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487825</v>
+        <v>487007</v>
       </c>
       <c r="R48" t="n">
-        <v>6979802</v>
+        <v>6979324</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5863,7 +5832,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5873,12 +5842,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>På gammal tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5893,44 +5862,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134637864</v>
+        <v>134637844</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5940,13 +5909,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487898</v>
+        <v>486955</v>
       </c>
       <c r="R49" t="n">
-        <v>6979887</v>
+        <v>6979311</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5975,7 +5944,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5985,12 +5954,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal tall</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6017,32 +5981,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134624375</v>
+        <v>134620466</v>
       </c>
       <c r="B50" t="n">
-        <v>106324</v>
+        <v>78776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6052,10 +6016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487599</v>
+        <v>487031</v>
       </c>
       <c r="R50" t="n">
-        <v>6979420</v>
+        <v>6979572</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6087,7 +6051,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6097,12 +6061,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På marken i tallskog</t>
+          <t>På gammal tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6129,10 +6093,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134637848</v>
+        <v>134620802</v>
       </c>
       <c r="B51" t="n">
-        <v>79405</v>
+        <v>83358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6140,37 +6104,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487137</v>
+        <v>486980</v>
       </c>
       <c r="R51" t="n">
-        <v>6979293</v>
+        <v>6979507</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6199,7 +6163,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6209,7 +6173,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6224,22 +6193,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134637842</v>
+        <v>134620885</v>
       </c>
       <c r="B52" t="n">
-        <v>91974</v>
+        <v>83358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6247,37 +6216,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486973</v>
+        <v>486951</v>
       </c>
       <c r="R52" t="n">
-        <v>6979366</v>
+        <v>6979512</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6306,7 +6275,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6316,7 +6285,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6331,22 +6305,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134619985</v>
+        <v>134620305</v>
       </c>
       <c r="B53" t="n">
-        <v>93271</v>
+        <v>79130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6354,37 +6328,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487125</v>
+        <v>487031</v>
       </c>
       <c r="R53" t="n">
-        <v>6979494</v>
+        <v>6979572</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6413,7 +6387,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6423,7 +6397,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6438,22 +6417,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134623562</v>
+        <v>134621634</v>
       </c>
       <c r="B54" t="n">
-        <v>93271</v>
+        <v>79130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,21 +6440,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6485,13 +6464,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487067</v>
+        <v>487047</v>
       </c>
       <c r="R54" t="n">
-        <v>6979518</v>
+        <v>6979362</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6520,7 +6499,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6530,7 +6509,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6545,44 +6529,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134637841</v>
+        <v>134637836</v>
       </c>
       <c r="B55" t="n">
-        <v>91937</v>
+        <v>79130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6592,10 +6576,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486988</v>
+        <v>486956</v>
       </c>
       <c r="R55" t="n">
-        <v>6979418</v>
+        <v>6979505</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -6627,7 +6611,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6637,7 +6621,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6664,48 +6648,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134620673</v>
+        <v>134637846</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487001</v>
+        <v>487136</v>
       </c>
       <c r="R56" t="n">
-        <v>6979537</v>
+        <v>6979298</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6734,7 +6718,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6744,12 +6728,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>45 cm långa bålar på gammal tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6764,69 +6743,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134620688</v>
+        <v>134620077</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79992</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486981</v>
+        <v>487120</v>
       </c>
       <c r="R57" t="n">
-        <v>6979523</v>
+        <v>6979507</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6855,7 +6825,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6865,7 +6835,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På rotben på gammal tallåga i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6880,57 +6855,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134621129</v>
+        <v>134620174</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79992</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486977</v>
+        <v>487035</v>
       </c>
       <c r="R58" t="n">
-        <v>6979380</v>
+        <v>6979565</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6962,7 +6937,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6972,12 +6947,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6997,52 +6972,52 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134621774</v>
+        <v>134620386</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487007</v>
+        <v>487031</v>
       </c>
       <c r="R59" t="n">
-        <v>6979324</v>
+        <v>6979572</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7074,7 +7049,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7084,12 +7059,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal tallskog</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7116,48 +7091,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134637844</v>
+        <v>134621552</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79992</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486955</v>
+        <v>487037</v>
       </c>
       <c r="R60" t="n">
-        <v>6979311</v>
+        <v>6979375</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7186,7 +7161,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7196,7 +7171,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7211,22 +7191,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134620466</v>
+        <v>134621604</v>
       </c>
       <c r="B61" t="n">
-        <v>78776</v>
+        <v>79992</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7234,34 +7214,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487031</v>
+        <v>487047</v>
       </c>
       <c r="R61" t="n">
-        <v>6979572</v>
+        <v>6979362</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7293,7 +7273,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7303,12 +7283,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7335,10 +7315,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134620802</v>
+        <v>134637835</v>
       </c>
       <c r="B62" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7346,37 +7326,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486980</v>
+        <v>486956</v>
       </c>
       <c r="R62" t="n">
-        <v>6979507</v>
+        <v>6979505</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7405,7 +7385,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7415,12 +7395,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7435,22 +7410,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134620885</v>
+        <v>134637839</v>
       </c>
       <c r="B63" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7458,37 +7433,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486951</v>
+        <v>486984</v>
       </c>
       <c r="R63" t="n">
-        <v>6979512</v>
+        <v>6979419</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7517,7 +7492,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7527,12 +7502,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal sumpgranskog</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7547,22 +7517,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134620305</v>
+        <v>134637845</v>
       </c>
       <c r="B64" t="n">
-        <v>79130</v>
+        <v>79992</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7570,37 +7540,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487031</v>
+        <v>487137</v>
       </c>
       <c r="R64" t="n">
-        <v>6979572</v>
+        <v>6979297</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7629,7 +7599,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7639,12 +7609,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7659,44 +7624,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134621634</v>
+        <v>134621423</v>
       </c>
       <c r="B65" t="n">
-        <v>79130</v>
+        <v>111153</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>220240</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7706,10 +7671,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487047</v>
+        <v>487018</v>
       </c>
       <c r="R65" t="n">
-        <v>6979362</v>
+        <v>6979338</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7741,7 +7706,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7751,12 +7716,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>Rikligt på marken i gammal stavatallskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7783,48 +7748,62 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134637836</v>
+        <v>134621349</v>
       </c>
       <c r="B66" t="n">
-        <v>79130</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486956</v>
+        <v>486975</v>
       </c>
       <c r="R66" t="n">
-        <v>6979505</v>
+        <v>6979371</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7853,7 +7832,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7863,7 +7842,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>17 skott, varav ett blommande, på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7878,60 +7862,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134637846</v>
+        <v>134622212</v>
       </c>
       <c r="B67" t="n">
-        <v>79130</v>
+        <v>106358</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>221157</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487136</v>
+        <v>487160</v>
       </c>
       <c r="R67" t="n">
-        <v>6979298</v>
+        <v>6979297</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7960,7 +7944,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7970,7 +7954,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7990,55 +7974,55 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134620077</v>
+        <v>134622977</v>
       </c>
       <c r="B68" t="n">
-        <v>79992</v>
+        <v>106309</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487120</v>
+        <v>487004</v>
       </c>
       <c r="R68" t="n">
-        <v>6979507</v>
+        <v>6979263</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8067,7 +8051,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8077,12 +8061,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På rotben på gammal tallåga i gammal hällmarkstallskog</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8097,44 +8076,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134620174</v>
+        <v>134620740</v>
       </c>
       <c r="B69" t="n">
-        <v>79992</v>
+        <v>98060</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8144,10 +8123,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487035</v>
+        <v>487009</v>
       </c>
       <c r="R69" t="n">
-        <v>6979565</v>
+        <v>6979527</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8179,7 +8158,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8189,12 +8168,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>På marken i i gammal tallskog på udde mot myr</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8214,55 +8193,55 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134620386</v>
+        <v>134637849</v>
       </c>
       <c r="B70" t="n">
-        <v>79992</v>
+        <v>99217</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487031</v>
+        <v>487158</v>
       </c>
       <c r="R70" t="n">
-        <v>6979572</v>
+        <v>6979235</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8291,7 +8270,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8301,12 +8280,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8321,60 +8295,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134621552</v>
+        <v>134637850</v>
       </c>
       <c r="B71" t="n">
-        <v>79992</v>
+        <v>99848</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>222302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487037</v>
+        <v>487015</v>
       </c>
       <c r="R71" t="n">
-        <v>6979375</v>
+        <v>6979263</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8403,7 +8377,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8413,12 +8387,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8433,22 +8402,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134621604</v>
+        <v>134620155</v>
       </c>
       <c r="B72" t="n">
-        <v>79992</v>
+        <v>79131</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8456,34 +8425,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487047</v>
+        <v>487035</v>
       </c>
       <c r="R72" t="n">
-        <v>6979362</v>
+        <v>6979565</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8515,7 +8484,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8525,12 +8494,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>På kolad ved på gammal bränd tallhögstubbe</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8550,17 +8519,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134637835</v>
+        <v>134620355</v>
       </c>
       <c r="B73" t="n">
-        <v>79992</v>
+        <v>79131</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,37 +8537,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486956</v>
+        <v>487031</v>
       </c>
       <c r="R73" t="n">
-        <v>6979505</v>
+        <v>6979572</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8627,7 +8596,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8637,7 +8606,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8652,22 +8626,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134637839</v>
+        <v>134621567</v>
       </c>
       <c r="B74" t="n">
-        <v>79992</v>
+        <v>79131</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8675,37 +8649,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486984</v>
+        <v>487037</v>
       </c>
       <c r="R74" t="n">
-        <v>6979419</v>
+        <v>6979375</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8734,7 +8708,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8744,7 +8718,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8759,22 +8738,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134637845</v>
+        <v>134621619</v>
       </c>
       <c r="B75" t="n">
-        <v>79992</v>
+        <v>79131</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8782,37 +8761,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487137</v>
+        <v>487047</v>
       </c>
       <c r="R75" t="n">
-        <v>6979297</v>
+        <v>6979362</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8841,7 +8820,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8851,7 +8830,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8866,22 +8850,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134620794</v>
+        <v>134637837</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8889,42 +8873,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486975</v>
+        <v>486956</v>
       </c>
       <c r="R76" t="n">
-        <v>6979500</v>
+        <v>6979505</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8953,7 +8932,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8963,12 +8942,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack och födosöksspår på gammal död gran</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8988,17 +8962,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134620818</v>
+        <v>134637840</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9006,42 +8980,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486974</v>
+        <v>486991</v>
       </c>
       <c r="R77" t="n">
-        <v>6979501</v>
+        <v>6979419</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9070,7 +9039,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9080,12 +9049,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9105,17 +9069,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134621085</v>
+        <v>134637847</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>79131</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9123,42 +9087,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486979</v>
+        <v>487136</v>
       </c>
       <c r="R78" t="n">
-        <v>6979382</v>
+        <v>6979298</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9187,7 +9146,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9197,12 +9156,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:57</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Relativt färska ringhack, rikligt, på gammal tall i kanten mot sumpskog</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9217,57 +9171,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134621423</v>
+        <v>134622346</v>
       </c>
       <c r="B79" t="n">
-        <v>111153</v>
+        <v>79645</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220240</v>
+        <v>229338</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Vårtig dynlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Micarea elachista</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Körb.) Coppins &amp; R.Sant.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487018</v>
+        <v>487155</v>
       </c>
       <c r="R79" t="n">
-        <v>6979338</v>
+        <v>6979276</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9299,7 +9253,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9309,12 +9263,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal stavatallskog</t>
+          <t>På tallhögstubbe/ dimensionsavverkningsstubbe i gammal tallskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9341,59 +9295,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134621349</v>
+        <v>134620767</v>
       </c>
       <c r="B80" t="n">
-        <v>99195</v>
+        <v>79396</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>260591</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486975</v>
+        <v>487013</v>
       </c>
       <c r="R80" t="n">
-        <v>6979371</v>
+        <v>6979545</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9425,7 +9365,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9435,12 +9375,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>17 skott, varav ett blommande, på marken i gammal barrblandskog</t>
+          <t>På gammal tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9467,48 +9407,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134622212</v>
+        <v>134621877</v>
       </c>
       <c r="B81" t="n">
-        <v>106358</v>
+        <v>79396</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221157</v>
+        <v>260591</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487160</v>
+        <v>487072</v>
       </c>
       <c r="R81" t="n">
-        <v>6979297</v>
+        <v>6979275</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9537,7 +9477,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9547,7 +9487,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På äldre gran i gammal tallskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9562,44 +9507,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134622977</v>
+        <v>134621948</v>
       </c>
       <c r="B82" t="n">
-        <v>106309</v>
+        <v>79396</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221725</v>
+        <v>260591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9609,13 +9554,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487004</v>
+        <v>487125</v>
       </c>
       <c r="R82" t="n">
-        <v>6979263</v>
+        <v>6979267</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9644,7 +9589,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9654,7 +9599,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På död tall i äldre tallskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9669,1558 +9619,15 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>134620740</v>
-      </c>
-      <c r="B83" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>487009</v>
-      </c>
-      <c r="R83" t="n">
-        <v>6979527</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På marken i i gammal tallskog på udde mot myr</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>134637849</v>
-      </c>
-      <c r="B84" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Yxskafttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>487158</v>
-      </c>
-      <c r="R84" t="n">
-        <v>6979235</v>
-      </c>
-      <c r="S84" t="n">
-        <v>5</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>134637850</v>
-      </c>
-      <c r="B85" t="n">
-        <v>99848</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>222302</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Spädstarr</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Carex disperma</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Dewey</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Yxskafttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>487015</v>
-      </c>
-      <c r="R85" t="n">
-        <v>6979263</v>
-      </c>
-      <c r="S85" t="n">
-        <v>5</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>134620155</v>
-      </c>
-      <c r="B86" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>487035</v>
-      </c>
-      <c r="R86" t="n">
-        <v>6979565</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>134620355</v>
-      </c>
-      <c r="B87" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>487031</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6979572</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>134621567</v>
-      </c>
-      <c r="B88" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>487037</v>
-      </c>
-      <c r="R88" t="n">
-        <v>6979375</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>134621619</v>
-      </c>
-      <c r="B89" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>487047</v>
-      </c>
-      <c r="R89" t="n">
-        <v>6979362</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>134637837</v>
-      </c>
-      <c r="B90" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Yxskafttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>486956</v>
-      </c>
-      <c r="R90" t="n">
-        <v>6979505</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>134637840</v>
-      </c>
-      <c r="B91" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Yxskafttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>486991</v>
-      </c>
-      <c r="R91" t="n">
-        <v>6979419</v>
-      </c>
-      <c r="S91" t="n">
-        <v>3</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>134637847</v>
-      </c>
-      <c r="B92" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Yxskafttjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>487136</v>
-      </c>
-      <c r="R92" t="n">
-        <v>6979298</v>
-      </c>
-      <c r="S92" t="n">
-        <v>3</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Ludvig Nordin</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>134622346</v>
-      </c>
-      <c r="B93" t="n">
-        <v>79645</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>229338</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Vårtig dynlav</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Micarea elachista</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Körb.) Coppins &amp; R.Sant.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>487155</v>
-      </c>
-      <c r="R93" t="n">
-        <v>6979276</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På tallhögstubbe/ dimensionsavverkningsstubbe i gammal tallskog</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>134620767</v>
-      </c>
-      <c r="B94" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>487013</v>
-      </c>
-      <c r="R94" t="n">
-        <v>6979545</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På gammal tall i gammal tallskog</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>134621877</v>
-      </c>
-      <c r="B95" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>487072</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6979275</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På äldre gran i gammal tallskog</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>134621948</v>
-      </c>
-      <c r="B96" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>487125</v>
-      </c>
-      <c r="R96" t="n">
-        <v>6979267</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På död tall i äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23145-2026 artfynd.xlsx
+++ b/artfynd/A 23145-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,48 +2241,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134637824</v>
+        <v>134623743</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487359</v>
+        <v>487295</v>
       </c>
       <c r="R16" t="n">
-        <v>6979505</v>
+        <v>6979474</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,7 +2316,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2321,12 +2326,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>Ringhack på tall som är mer än 150 år</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,34 +2351,34 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134637825</v>
+        <v>134637821</v>
       </c>
       <c r="B17" t="n">
-        <v>58131</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2388,10 +2393,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487356</v>
+        <v>487291</v>
       </c>
       <c r="R17" t="n">
-        <v>6979504</v>
+        <v>6979650</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2423,7 +2428,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2433,12 +2438,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 ex lockläte</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,57 +2470,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134623869</v>
+        <v>134637822</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487389</v>
+        <v>487293</v>
       </c>
       <c r="R18" t="n">
-        <v>6979494</v>
+        <v>6979657</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2554,12 +2550,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>+2 vinterståndare</t>
+          <t>Ringhack på gran, äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,55 +2575,55 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134618835</v>
+        <v>134637823</v>
       </c>
       <c r="B19" t="n">
-        <v>107695</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221705</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Melampyrum pratense</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487284</v>
+        <v>487313</v>
       </c>
       <c r="R19" t="n">
-        <v>6979439</v>
+        <v>6979635</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2656,7 +2652,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2666,7 +2662,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,17 +2687,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134618455</v>
+        <v>134637824</v>
       </c>
       <c r="B20" t="n">
-        <v>106309</v>
+        <v>57162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,51 +2705,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>487359</v>
       </c>
       <c r="R20" t="n">
-        <v>6979628</v>
+        <v>6979505</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2777,7 +2764,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,12 +2774,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I äldre barrblandskog</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,22 +2794,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134618336</v>
+        <v>134637825</v>
       </c>
       <c r="B21" t="n">
-        <v>99217</v>
+        <v>58131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,37 +2817,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>103023</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487347</v>
+        <v>487356</v>
       </c>
       <c r="R21" t="n">
-        <v>6979670</v>
+        <v>6979504</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2889,7 +2876,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,12 +2886,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i äldre barrblandskog</t>
+          <t>1 ex lockläte</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,60 +2906,69 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134637820</v>
+        <v>134623869</v>
       </c>
       <c r="B22" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487275</v>
+        <v>487389</v>
       </c>
       <c r="R22" t="n">
-        <v>6979637</v>
+        <v>6979494</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3007,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>+2 vinterståndare</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,17 +3032,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134637827</v>
+        <v>134618835</v>
       </c>
       <c r="B23" t="n">
-        <v>99217</v>
+        <v>107695</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,37 +3050,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>221705</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487313</v>
+        <v>487284</v>
       </c>
       <c r="R23" t="n">
-        <v>6979509</v>
+        <v>6979439</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3108,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,17 +3139,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134618965</v>
+        <v>134618455</v>
       </c>
       <c r="B24" t="n">
-        <v>99872</v>
+        <v>106309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,37 +3157,51 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222316</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klotstarr</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex globularis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487284</v>
+        <v>487359</v>
       </c>
       <c r="R24" t="n">
-        <v>6979439</v>
+        <v>6979628</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3215,7 +3230,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3225,7 +3240,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,60 +3260,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134637828</v>
+        <v>134618336</v>
       </c>
       <c r="B25" t="n">
-        <v>78382</v>
+        <v>99217</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487317</v>
+        <v>487347</v>
       </c>
       <c r="R25" t="n">
-        <v>6979494</v>
+        <v>6979670</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3322,7 +3342,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3332,7 +3352,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På marken i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,22 +3372,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134618485</v>
+        <v>134637820</v>
       </c>
       <c r="B26" t="n">
-        <v>80444</v>
+        <v>99217</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3370,37 +3395,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229748</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487357</v>
+        <v>487275</v>
       </c>
       <c r="R26" t="n">
-        <v>6979618</v>
+        <v>6979637</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3429,7 +3454,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3439,12 +3464,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På grov sälglåga i äldre barrblandskog</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3459,60 +3479,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134619363</v>
+        <v>134637827</v>
       </c>
       <c r="B27" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487218</v>
+        <v>487313</v>
       </c>
       <c r="R27" t="n">
-        <v>6979401</v>
+        <v>6979509</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3541,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3551,12 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen tall på talludde vid myr</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,60 +3586,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134637834</v>
+        <v>134618965</v>
       </c>
       <c r="B28" t="n">
-        <v>79396</v>
+        <v>99872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>260591</v>
+        <v>222316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Klotstarr</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carex globularis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487224</v>
+        <v>487284</v>
       </c>
       <c r="R28" t="n">
-        <v>6979397</v>
+        <v>6979439</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3653,7 +3668,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3663,7 +3678,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3683,17 +3698,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134624022</v>
+        <v>134637828</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>78382</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3701,37 +3716,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487514</v>
+        <v>487317</v>
       </c>
       <c r="R29" t="n">
-        <v>6979419</v>
+        <v>6979494</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3760,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3770,12 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På dimensionsavverkningsstubbe av tall</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3795,55 +3805,55 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134637854</v>
+        <v>134618485</v>
       </c>
       <c r="B30" t="n">
-        <v>93271</v>
+        <v>80444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>229748</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487622</v>
+        <v>487357</v>
       </c>
       <c r="R30" t="n">
-        <v>6979627</v>
+        <v>6979618</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3872,7 +3882,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3882,7 +3892,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På grov sälglåga i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3897,60 +3912,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134637857</v>
+        <v>134619363</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79396</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>260591</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487632</v>
+        <v>487218</v>
       </c>
       <c r="R31" t="n">
-        <v>6979790</v>
+        <v>6979401</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,7 +3994,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3989,7 +4004,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen tall på talludde vid myr</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4004,44 +4024,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134637858</v>
+        <v>134637834</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79396</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>260591</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4051,10 +4071,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487643</v>
+        <v>487224</v>
       </c>
       <c r="R32" t="n">
-        <v>6979820</v>
+        <v>6979397</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4086,7 +4106,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4096,7 +4116,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4123,10 +4143,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134624193</v>
+        <v>134624022</v>
       </c>
       <c r="B33" t="n">
-        <v>83358</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4134,21 +4154,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4158,13 +4178,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487554</v>
+        <v>487514</v>
       </c>
       <c r="R33" t="n">
-        <v>6979356</v>
+        <v>6979419</v>
       </c>
       <c r="S33" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4193,7 +4213,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4203,12 +4223,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4223,22 +4243,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134637853</v>
+        <v>134637854</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>93271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4246,21 +4266,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4270,13 +4290,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>487630</v>
+        <v>487622</v>
       </c>
       <c r="R34" t="n">
-        <v>6979597</v>
+        <v>6979627</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4342,48 +4362,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134624138</v>
+        <v>134637857</v>
       </c>
       <c r="B35" t="n">
-        <v>80382</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487554</v>
+        <v>487632</v>
       </c>
       <c r="R35" t="n">
-        <v>6979356</v>
+        <v>6979790</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4412,7 +4432,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4422,12 +4442,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,44 +4457,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134637851</v>
+        <v>134637858</v>
       </c>
       <c r="B36" t="n">
-        <v>80492</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4489,13 +4504,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487604</v>
+        <v>487643</v>
       </c>
       <c r="R36" t="n">
-        <v>6979461</v>
+        <v>6979820</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4524,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4534,7 +4549,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4561,48 +4576,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134637852</v>
+        <v>134624193</v>
       </c>
       <c r="B37" t="n">
-        <v>80492</v>
+        <v>83358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487630</v>
+        <v>487554</v>
       </c>
       <c r="R37" t="n">
-        <v>6979578</v>
+        <v>6979356</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4631,7 +4646,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4641,7 +4656,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4656,44 +4676,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134637863</v>
+        <v>134637853</v>
       </c>
       <c r="B38" t="n">
-        <v>80492</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4703,13 +4723,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487854</v>
+        <v>487630</v>
       </c>
       <c r="R38" t="n">
-        <v>6979801</v>
+        <v>6979597</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4738,7 +4758,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4748,7 +4768,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,10 +4795,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134624375</v>
+        <v>134624138</v>
       </c>
       <c r="B39" t="n">
-        <v>106324</v>
+        <v>80382</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4786,21 +4806,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4810,10 +4830,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487599</v>
+        <v>487554</v>
       </c>
       <c r="R39" t="n">
-        <v>6979420</v>
+        <v>6979356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4865,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4875,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På marken i tallskog</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4887,32 +4907,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134637848</v>
+        <v>134637851</v>
       </c>
       <c r="B40" t="n">
-        <v>79405</v>
+        <v>80492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4922,13 +4942,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487137</v>
+        <v>487604</v>
       </c>
       <c r="R40" t="n">
-        <v>6979293</v>
+        <v>6979461</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4957,7 +4977,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4967,7 +4987,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,32 +5014,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134637842</v>
+        <v>134637852</v>
       </c>
       <c r="B41" t="n">
-        <v>91974</v>
+        <v>80492</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5029,13 +5049,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486973</v>
+        <v>487630</v>
       </c>
       <c r="R41" t="n">
-        <v>6979366</v>
+        <v>6979578</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5064,7 +5084,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5074,7 +5094,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5101,48 +5121,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134619985</v>
+        <v>134637863</v>
       </c>
       <c r="B42" t="n">
-        <v>93271</v>
+        <v>80492</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487125</v>
+        <v>487854</v>
       </c>
       <c r="R42" t="n">
-        <v>6979494</v>
+        <v>6979801</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5171,7 +5191,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5181,7 +5201,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5201,17 +5221,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134623562</v>
+        <v>134624216</v>
       </c>
       <c r="B43" t="n">
-        <v>93271</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,37 +5239,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487067</v>
+        <v>487587</v>
       </c>
       <c r="R43" t="n">
-        <v>6979518</v>
+        <v>6979388</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5278,7 +5303,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5288,7 +5313,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5303,44 +5333,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134637841</v>
+        <v>134637856</v>
       </c>
       <c r="B44" t="n">
-        <v>91937</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5350,13 +5380,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486988</v>
+        <v>487583</v>
       </c>
       <c r="R44" t="n">
-        <v>6979418</v>
+        <v>6979673</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,7 +5415,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5395,7 +5425,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,48 +5457,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134620673</v>
+        <v>134637859</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487001</v>
+        <v>487804</v>
       </c>
       <c r="R45" t="n">
-        <v>6979537</v>
+        <v>6979778</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,7 +5527,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5502,12 +5537,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>45 cm långa bålar på gammal tall</t>
+          <t>Ringhack på gammal tall, äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5522,69 +5557,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134620688</v>
+        <v>134637860</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486981</v>
+        <v>487809</v>
       </c>
       <c r="R46" t="n">
-        <v>6979523</v>
+        <v>6979778</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5613,7 +5639,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5623,7 +5649,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tall, äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5643,55 +5674,55 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134621129</v>
+        <v>134637861</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486977</v>
+        <v>487825</v>
       </c>
       <c r="R47" t="n">
-        <v>6979380</v>
+        <v>6979774</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5720,7 +5751,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5730,12 +5761,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran i gransumpskog</t>
+          <t>Ringhack på gammal tall, äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5750,60 +5781,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134621774</v>
+        <v>134637862</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487007</v>
+        <v>487825</v>
       </c>
       <c r="R48" t="n">
-        <v>6979324</v>
+        <v>6979802</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5832,7 +5863,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5842,12 +5873,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal tallskog</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5862,44 +5893,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134637844</v>
+        <v>134637864</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5909,13 +5940,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486955</v>
+        <v>487898</v>
       </c>
       <c r="R49" t="n">
-        <v>6979311</v>
+        <v>6979887</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5944,7 +5975,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5954,7 +5985,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,32 +6017,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134620466</v>
+        <v>134624375</v>
       </c>
       <c r="B50" t="n">
-        <v>78776</v>
+        <v>106324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6437</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6016,10 +6052,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487031</v>
+        <v>487599</v>
       </c>
       <c r="R50" t="n">
-        <v>6979572</v>
+        <v>6979420</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6051,7 +6087,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6061,12 +6097,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>På marken i tallskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,10 +6129,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134620802</v>
+        <v>134637848</v>
       </c>
       <c r="B51" t="n">
-        <v>83358</v>
+        <v>79405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6104,37 +6140,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486980</v>
+        <v>487137</v>
       </c>
       <c r="R51" t="n">
-        <v>6979507</v>
+        <v>6979293</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6163,7 +6199,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6173,12 +6209,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6193,22 +6224,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134620885</v>
+        <v>134637842</v>
       </c>
       <c r="B52" t="n">
-        <v>83358</v>
+        <v>91974</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6216,37 +6247,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486951</v>
+        <v>486973</v>
       </c>
       <c r="R52" t="n">
-        <v>6979512</v>
+        <v>6979366</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6275,7 +6306,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6285,12 +6316,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal sumpgranskog</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6305,22 +6331,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134620305</v>
+        <v>134619985</v>
       </c>
       <c r="B53" t="n">
-        <v>79130</v>
+        <v>93271</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6328,37 +6354,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487031</v>
+        <v>487125</v>
       </c>
       <c r="R53" t="n">
-        <v>6979572</v>
+        <v>6979494</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6387,7 +6413,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6397,12 +6423,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6417,22 +6438,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134621634</v>
+        <v>134623562</v>
       </c>
       <c r="B54" t="n">
-        <v>79130</v>
+        <v>93271</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6440,21 +6461,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6464,13 +6485,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487047</v>
+        <v>487067</v>
       </c>
       <c r="R54" t="n">
-        <v>6979362</v>
+        <v>6979518</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6499,7 +6520,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6509,12 +6530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6529,44 +6545,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134637836</v>
+        <v>134637841</v>
       </c>
       <c r="B55" t="n">
-        <v>79130</v>
+        <v>91937</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6576,10 +6592,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486956</v>
+        <v>486988</v>
       </c>
       <c r="R55" t="n">
-        <v>6979505</v>
+        <v>6979418</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -6611,7 +6627,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6621,7 +6637,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6648,48 +6664,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134637846</v>
+        <v>134620673</v>
       </c>
       <c r="B56" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487136</v>
+        <v>487001</v>
       </c>
       <c r="R56" t="n">
-        <v>6979298</v>
+        <v>6979537</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6718,7 +6734,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6728,7 +6744,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>45 cm långa bålar på gammal tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6743,60 +6764,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134620077</v>
+        <v>134620688</v>
       </c>
       <c r="B57" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487120</v>
+        <v>486981</v>
       </c>
       <c r="R57" t="n">
-        <v>6979507</v>
+        <v>6979523</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6825,7 +6855,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6835,12 +6865,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På rotben på gammal tallåga i gammal hällmarkstallskog</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6855,57 +6880,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134620174</v>
+        <v>134621129</v>
       </c>
       <c r="B58" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487035</v>
+        <v>486977</v>
       </c>
       <c r="R58" t="n">
-        <v>6979565</v>
+        <v>6979380</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6937,7 +6962,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6947,12 +6972,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>På gammal gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,52 +6997,52 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134620386</v>
+        <v>134621774</v>
       </c>
       <c r="B59" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487031</v>
+        <v>487007</v>
       </c>
       <c r="R59" t="n">
-        <v>6979572</v>
+        <v>6979324</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7049,7 +7074,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7059,12 +7084,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>På gammal tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7091,48 +7116,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134621552</v>
+        <v>134637844</v>
       </c>
       <c r="B60" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487037</v>
+        <v>486955</v>
       </c>
       <c r="R60" t="n">
-        <v>6979375</v>
+        <v>6979311</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7161,7 +7186,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7171,12 +7196,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7191,22 +7211,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134621604</v>
+        <v>134620466</v>
       </c>
       <c r="B61" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7214,34 +7234,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487047</v>
+        <v>487031</v>
       </c>
       <c r="R61" t="n">
-        <v>6979362</v>
+        <v>6979572</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7273,7 +7293,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7283,12 +7303,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>På gammal tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7315,10 +7335,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134637835</v>
+        <v>134620802</v>
       </c>
       <c r="B62" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7326,37 +7346,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486956</v>
+        <v>486980</v>
       </c>
       <c r="R62" t="n">
-        <v>6979505</v>
+        <v>6979507</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7385,7 +7405,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7395,7 +7415,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7410,22 +7435,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134637839</v>
+        <v>134620885</v>
       </c>
       <c r="B63" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7433,37 +7458,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486984</v>
+        <v>486951</v>
       </c>
       <c r="R63" t="n">
-        <v>6979419</v>
+        <v>6979512</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7492,7 +7517,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7502,7 +7527,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7517,22 +7547,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134637845</v>
+        <v>134620305</v>
       </c>
       <c r="B64" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7540,37 +7570,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487137</v>
+        <v>487031</v>
       </c>
       <c r="R64" t="n">
-        <v>6979297</v>
+        <v>6979572</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7599,7 +7629,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7609,7 +7639,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7624,44 +7659,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134621423</v>
+        <v>134621634</v>
       </c>
       <c r="B65" t="n">
-        <v>111153</v>
+        <v>79130</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220240</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7671,10 +7706,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487018</v>
+        <v>487047</v>
       </c>
       <c r="R65" t="n">
-        <v>6979338</v>
+        <v>6979362</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7706,7 +7741,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7716,12 +7751,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt på marken i gammal stavatallskog</t>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7748,62 +7783,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134621349</v>
+        <v>134637836</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>79130</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>486975</v>
+        <v>486956</v>
       </c>
       <c r="R66" t="n">
-        <v>6979371</v>
+        <v>6979505</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7832,7 +7853,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7842,12 +7863,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>17 skott, varav ett blommande, på marken i gammal barrblandskog</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7862,60 +7878,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134622212</v>
+        <v>134637846</v>
       </c>
       <c r="B67" t="n">
-        <v>106358</v>
+        <v>79130</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221157</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487160</v>
+        <v>487136</v>
       </c>
       <c r="R67" t="n">
-        <v>6979297</v>
+        <v>6979298</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7944,7 +7960,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7954,7 +7970,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,55 +7990,55 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134622977</v>
+        <v>134620077</v>
       </c>
       <c r="B68" t="n">
-        <v>106309</v>
+        <v>79992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487004</v>
+        <v>487120</v>
       </c>
       <c r="R68" t="n">
-        <v>6979263</v>
+        <v>6979507</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8051,7 +8067,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8061,7 +8077,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rotben på gammal tallåga i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8076,44 +8097,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134620740</v>
+        <v>134620174</v>
       </c>
       <c r="B69" t="n">
-        <v>98060</v>
+        <v>79992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8123,10 +8144,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487009</v>
+        <v>487035</v>
       </c>
       <c r="R69" t="n">
-        <v>6979527</v>
+        <v>6979565</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8158,7 +8179,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8168,12 +8189,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På marken i i gammal tallskog på udde mot myr</t>
+          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8193,55 +8214,55 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134637849</v>
+        <v>134620386</v>
       </c>
       <c r="B70" t="n">
-        <v>99217</v>
+        <v>79992</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487158</v>
+        <v>487031</v>
       </c>
       <c r="R70" t="n">
-        <v>6979235</v>
+        <v>6979572</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8270,7 +8291,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8280,7 +8301,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallhögstubbe i gammal hällmarkstallskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8295,60 +8321,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134637850</v>
+        <v>134621552</v>
       </c>
       <c r="B71" t="n">
-        <v>99848</v>
+        <v>79992</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222302</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487015</v>
+        <v>487037</v>
       </c>
       <c r="R71" t="n">
-        <v>6979263</v>
+        <v>6979375</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8377,7 +8403,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8387,7 +8413,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8402,22 +8433,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134620155</v>
+        <v>134621604</v>
       </c>
       <c r="B72" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8425,34 +8456,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487035</v>
+        <v>487047</v>
       </c>
       <c r="R72" t="n">
-        <v>6979565</v>
+        <v>6979362</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8484,7 +8515,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8494,12 +8525,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe</t>
+          <t>På kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8519,17 +8550,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134620355</v>
+        <v>134637835</v>
       </c>
       <c r="B73" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8537,37 +8568,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487031</v>
+        <v>486956</v>
       </c>
       <c r="R73" t="n">
-        <v>6979572</v>
+        <v>6979505</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8596,7 +8627,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8606,12 +8637,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8626,22 +8652,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134621567</v>
+        <v>134637839</v>
       </c>
       <c r="B74" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8649,37 +8675,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487037</v>
+        <v>486984</v>
       </c>
       <c r="R74" t="n">
-        <v>6979375</v>
+        <v>6979419</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8708,7 +8734,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8718,12 +8744,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8738,22 +8759,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134621619</v>
+        <v>134637845</v>
       </c>
       <c r="B75" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8761,37 +8782,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487047</v>
+        <v>487137</v>
       </c>
       <c r="R75" t="n">
-        <v>6979362</v>
+        <v>6979297</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8820,7 +8841,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8830,12 +8851,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På kolad tallhögstubbe</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8850,22 +8866,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134637837</v>
+        <v>134620794</v>
       </c>
       <c r="B76" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8873,37 +8889,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486956</v>
+        <v>486975</v>
       </c>
       <c r="R76" t="n">
-        <v>6979505</v>
+        <v>6979500</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8932,7 +8953,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8942,7 +8963,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack och födosöksspår på gammal död gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8962,17 +8988,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134637840</v>
+        <v>134620818</v>
       </c>
       <c r="B77" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8980,37 +9006,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486991</v>
+        <v>486974</v>
       </c>
       <c r="R77" t="n">
-        <v>6979419</v>
+        <v>6979501</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9039,7 +9070,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9049,7 +9080,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9069,17 +9105,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134637847</v>
+        <v>134621085</v>
       </c>
       <c r="B78" t="n">
-        <v>79131</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9087,37 +9123,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Yxskafttjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487136</v>
+        <v>486979</v>
       </c>
       <c r="R78" t="n">
-        <v>6979298</v>
+        <v>6979382</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9146,7 +9187,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9156,7 +9197,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Relativt färska ringhack, rikligt, på gammal tall i kanten mot sumpskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9171,57 +9217,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134622346</v>
+        <v>134621423</v>
       </c>
       <c r="B79" t="n">
-        <v>79645</v>
+        <v>111153</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229338</v>
+        <v>220240</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vårtig dynlav</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Micarea elachista</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Körb.) Coppins &amp; R.Sant.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487155</v>
+        <v>487018</v>
       </c>
       <c r="R79" t="n">
-        <v>6979276</v>
+        <v>6979338</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9253,7 +9299,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9263,12 +9309,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På tallhögstubbe/ dimensionsavverkningsstubbe i gammal tallskog</t>
+          <t>Rikligt på marken i gammal stavatallskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9295,45 +9341,59 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134620767</v>
+        <v>134621349</v>
       </c>
       <c r="B80" t="n">
-        <v>79396</v>
+        <v>99195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487013</v>
+        <v>486975</v>
       </c>
       <c r="R80" t="n">
-        <v>6979545</v>
+        <v>6979371</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9365,7 +9425,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9375,12 +9435,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal tall i gammal tallskog</t>
+          <t>17 skott, varav ett blommande, på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9407,48 +9467,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134621877</v>
+        <v>134622212</v>
       </c>
       <c r="B81" t="n">
-        <v>79396</v>
+        <v>106358</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>260591</v>
+        <v>221157</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+          <t>Lill-Mörttjärnen, Lill-Mörttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487072</v>
+        <v>487160</v>
       </c>
       <c r="R81" t="n">
-        <v>6979275</v>
+        <v>6979297</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9477,7 +9537,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9487,12 +9547,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På äldre gran i gammal tallskog</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9507,44 +9562,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134621948</v>
+        <v>134622977</v>
       </c>
       <c r="B82" t="n">
-        <v>79396</v>
+        <v>106309</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>260591</v>
+        <v>221725</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9554,13 +9609,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487125</v>
+        <v>487004</v>
       </c>
       <c r="R82" t="n">
-        <v>6979267</v>
+        <v>6979263</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9589,7 +9644,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9599,12 +9654,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På död tall i äldre tallskog</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9619,15 +9669,1558 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134620740</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>487009</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6979527</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På marken i i gammal tallskog på udde mot myr</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
           <t>Fredrik Jonsson</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
+      <c r="AX83" t="inlineStr">
         <is>
           <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
-      <c r="AY82" t="inlineStr"/>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134637849</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>487158</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6979235</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134637850</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99848</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>487015</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6979263</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134620155</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>487035</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6979565</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134620355</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>487031</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6979572</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal bränd tallhögstubbe i gammal hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134621567</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>487037</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6979375</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134621619</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>487047</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6979362</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På kolad tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134637837</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>486956</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6979505</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>134637840</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>486991</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6979419</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134637847</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>487136</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6979298</v>
+      </c>
+      <c r="S92" t="n">
+        <v>3</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>134622346</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79645</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229338</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vårtig dynlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Micarea elachista</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Körb.) Coppins &amp; R.Sant.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>487155</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6979276</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På tallhögstubbe/ dimensionsavverkningsstubbe i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134620767</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>487013</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6979545</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På gammal tall i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134621877</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>487072</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6979275</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På äldre gran i gammal tallskog</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134621948</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Sockentjärnen, Sockentjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>487125</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6979267</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På död tall i äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23145-2026 artfynd.xlsx
+++ b/artfynd/A 23145-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134623790</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618041</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618735</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637829</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134619355</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637833</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618070</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618233</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,6 +1850,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618643</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618244</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618346</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134623836</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2238,6 +2308,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637826</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2355,6 +2430,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134623743</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2467,6 +2547,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637821</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2579,6 +2664,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637822</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2691,6 +2781,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637823</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2803,6 +2898,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637824</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2915,6 +3015,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637825</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3036,6 +3141,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134623869</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3143,6 +3253,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618835</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3269,6 +3384,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618455</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3381,6 +3501,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618336</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3488,6 +3613,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637820</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3595,6 +3725,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637827</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3702,6 +3837,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618965</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3809,6 +3949,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637828</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3921,6 +4066,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134618485</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4033,6 +4183,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134619363</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4140,6 +4295,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637834</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4252,6 +4412,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624022</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4359,6 +4524,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637854</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4466,6 +4636,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637857</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4573,6 +4748,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637858</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4685,6 +4865,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624193</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4792,6 +4977,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637853</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4904,6 +5094,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624138</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5011,6 +5206,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637851</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5118,6 +5318,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637852</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5225,6 +5430,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637863</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5342,6 +5552,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624216</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5454,6 +5669,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637856</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5566,6 +5786,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637859</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5678,6 +5903,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637860</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5790,6 +6020,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637861</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5902,6 +6137,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637862</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6014,6 +6254,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637864</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6126,6 +6371,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134624375</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6233,6 +6483,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637848</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6340,6 +6595,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637842</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6447,6 +6707,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134619985</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6554,6 +6819,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134623562</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6661,6 +6931,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637841</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6773,6 +7048,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620673</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6889,6 +7169,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620688</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7001,6 +7286,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621129</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7113,6 +7403,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621774</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7220,6 +7515,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637844</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7332,6 +7632,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620466</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7444,6 +7749,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620802</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7556,6 +7866,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620885</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7668,6 +7983,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620305</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7780,6 +8100,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621634</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7887,6 +8212,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637836</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7994,6 +8324,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637846</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8106,6 +8441,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620077</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8218,6 +8558,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620174</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8330,6 +8675,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620386</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8442,6 +8792,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621552</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8554,6 +8909,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621604</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8661,6 +9021,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637835</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8768,6 +9133,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637839</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8875,6 +9245,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637845</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8992,6 +9367,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620794</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9109,6 +9489,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620818</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9226,6 +9611,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621085</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9338,6 +9728,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621423</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9464,6 +9859,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621349</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9571,6 +9971,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134622212</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9678,6 +10083,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134622977</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9790,6 +10200,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620740</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9897,6 +10312,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637849</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10004,6 +10424,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637850</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10116,6 +10541,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620155</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10228,6 +10658,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620355</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10340,6 +10775,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621567</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10452,6 +10892,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621619</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10559,6 +11004,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637837</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10666,6 +11116,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637840</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10773,6 +11228,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637847</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10885,6 +11345,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134622346</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10997,6 +11462,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134620767</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11109,6 +11579,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621877</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11221,8 +11696,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134621948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23145-2026 artfynd.xlsx
+++ b/artfynd/A 23145-2026 artfynd.xlsx
@@ -2319,7 +2319,7 @@
         <v>134623743</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>134637821</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>134637822</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>134637823</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>134624216</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>134637856</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>134637859</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>134637860</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>134637861</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>134637862</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>134637864</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>134620794</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>134620818</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>134621085</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
